--- a/quizzes/045_how_well_do_you_know_your_partner_quiz--quizzes.xlsx
+++ b/quizzes/045_how_well_do_you_know_your_partner_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>first_question</t>
+          <t>partner_favourite_food</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>first_question</t>
+          <t>What's your partner's favorite food?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>favorite_food</t>
+          <t>partner_hobbies</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>favorite_food</t>
+          <t>Does your partner have a favorite hobby?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>partner_interests</t>
+          <t>partner_employment_status</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>partner_interests</t>
+          <t>How well do you know your partner's employment status?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>partner_employment_status</t>
+          <t>partner_favorite_music</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>partner_employment_status</t>
+          <t>What's your partner's favorite music genre?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>partner_education_level</t>
+          <t>partner_favorite_holiday_destination</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>partner_education_level</t>
+          <t>What's your partner's favorite holiday destination?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>partner_workplace</t>
+          <t>partner_favorite_movie</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>partner_workplace</t>
+          <t>Does your partner enjoy watching movies?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>partner_favorite_hobby</t>
+          <t>partner_favorite_book</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>favorite_hobby</t>
+          <t>What's your partner's favorite book?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>partner_occupation</t>
+          <t>partner_favorite_color</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>partner_occupation</t>
+          <t>Does your partner have a favorite color?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>partner_favorite_color</t>
+          <t>partner_favorite_sport</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>favorite_color</t>
+          <t>Does your partner enjoy playing sports?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>partner_favorite_music</t>
+          <t>partner_favorite_instrument</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>favorite_music</t>
+          <t>What's your partner's favorite music instrument?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>partner_favorite_food</t>
+          <t>partner_favorite_destination</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>favorite_food</t>
+          <t>Has your partner traveled to their favorite destination?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,407 +773,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>partner_favourite_drink</t>
+          <t>partner_favorite_travel_destination</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>favorite_drink</t>
+          <t>What's your partner's favorite travel destination?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>partner_hobbies</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>favorite_hobbies</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>partner_favorite_movie</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>favorite_movie</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>partner_favorite_sport</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>favorite_sport</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>partner_favorite_book</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>favorite_book</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>partner_favorite_band</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>favorite_band</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>partner_favorite_travel_destination</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>favorite_travel_destination</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>partner_favorite_music_genre</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>favorite_music_genre</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>partner_favorite_hobby</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>favorite_hobby</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>partner_hobbies</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>hobbies</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>partner_favorite_holiday</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>favorite_holiday</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>partner_favorite_holiday_trip</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>favorite_holiday_trip</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>partner_favourite_drink</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>favourite_drink</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>partner_employed</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>employed</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>partner_edu</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>education</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>partner_hobbies</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>partner_hobbies</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>partner_education</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>partner_education</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>partner_favourite_sport</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>favorite_sport</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1193,9 +802,9 @@
   <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1218,629 +827,629 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>first_question_choices</t>
+          <t>partner_favourite_food_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Apple</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>first_question_choices</t>
+          <t>partner_favourite_food_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>pizza</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Pizza</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>favorite_food_choices</t>
+          <t>partner_favourite_food_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>sushi</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Sushi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>favorite_food_choices</t>
+          <t>partner_favourite_food_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>burgers</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Burgers</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>partner_employment_status_choices</t>
+          <t>partner_favourite_food_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'employed',_'value':_'employed'}</t>
+          <t>salad</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Employed', 'value': 'employed'}</t>
+          <t>Salad</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>partner_employment_status_choices</t>
+          <t>partner_hobbies_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'student',_'value':_'student'}</t>
+          <t>hiking</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Student', 'value': 'student'}</t>
+          <t>Hiking</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>partner_employment_status_choices</t>
+          <t>partner_hobbies_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'retired',_'value':_'retired'}</t>
+          <t>reading</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Retired', 'value': 'retired'}</t>
+          <t>Reading</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>partner_employment_status_choices</t>
+          <t>partner_hobbies_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'disabled',_'value':_'disabled'}</t>
+          <t>sports</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Disabled', 'value': 'disabled'}</t>
+          <t>Sports</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>partner_education_level_choices</t>
+          <t>partner_hobbies_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'primary',_'value':_'primary'}</t>
+          <t>traveling</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Primary', 'value': 'primary'}</t>
+          <t>Traveling</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>partner_education_level_choices</t>
+          <t>partner_hobbies_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'secondary',_'value':_'secondary'}</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Secondary', 'value': 'secondary'}</t>
+          <t>Music</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>partner_education_level_choices</t>
+          <t>partner_employment_status_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'high',_'value':_'high'}</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'High', 'value': 'high'}</t>
+          <t>Employed</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>partner_education_level_choices</t>
+          <t>partner_employment_status_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'some_college',_'value':_'some_college'}</t>
+          <t>unemployed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Some College', 'value': 'some_college'}</t>
+          <t>Unemployed</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>partner_education_level_choices</t>
+          <t>partner_employment_status_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_"bachelor's",_'value':_'bachelors'}</t>
+          <t>student</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': "Bachelor's", 'value': 'bachelors'}</t>
+          <t>Student</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>partner_education_level_choices</t>
+          <t>partner_employment_status_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_"master's",_'value':_'masters'}</t>
+          <t>retired</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': "Master's", 'value': 'masters'}</t>
+          <t>Retired</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>partner_education_level_choices</t>
+          <t>partner_employment_status_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'doctorate',_'value':_'doctorate'}</t>
+          <t>disabled</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Doctorate', 'value': 'doctorate'}</t>
+          <t>Disabled</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>partner_education_level_choices</t>
+          <t>partner_favorite_music_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'other',_'value':_'other'}</t>
+          <t>pop</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'Other', 'value': 'other'}</t>
+          <t>Pop</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>partner_hobbies_choices</t>
+          <t>partner_favorite_music_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>rock</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Rock</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>partner_hobbies_choices</t>
+          <t>partner_favorite_music_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>classical</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Classical</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>partner_hobbies_choices</t>
+          <t>partner_favorite_music_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>jazz</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Jazz</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>partner_hobbies_choices</t>
+          <t>partner_favorite_music_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>electronic</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Electronic</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>partner_employed_choices</t>
+          <t>partner_favorite_holiday_destination_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_true}</t>
+          <t>beach</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': True}</t>
+          <t>Beach</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>partner_employed_choices</t>
+          <t>partner_favorite_holiday_destination_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_false}</t>
+          <t>mountain</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': False}</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>partner_edu_choices</t>
+          <t>partner_favorite_holiday_destination_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_9,_'label':_'employed',_'value':_'employed'}</t>
+          <t>city</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 9, 'label': 'Employed', 'value': 'employed'}</t>
+          <t>City</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>partner_edu_choices</t>
+          <t>partner_favorite_holiday_destination_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'self',_'value':_'self'}</t>
+          <t>park</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'Self', 'value': 'self'}</t>
+          <t>Park</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>partner_edu_choices</t>
+          <t>partner_favorite_holiday_destination_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'retired',_'value':_'retired'}</t>
+          <t>lake</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'Retired', 'value': 'retired'}</t>
+          <t>Lake</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>partner_edu_choices</t>
+          <t>partner_favorite_movie_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_12,_'label':_'disabled',_'value':_'disabled'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 12, 'label': 'Disabled', 'value': 'disabled'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>partner_edu_choices</t>
+          <t>partner_favorite_movie_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_13,_'label':_'deceased',_'value':_'deceased'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 13, 'label': 'Deceased', 'value': 'deceased'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>partner_edu_choices</t>
+          <t>partner_favorite_color_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_14,_'label':_'unemployed',_'value':_'unemployed'}</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 14, 'label': 'Unemployed', 'value': 'unemployed'}</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>partner_edu_choices</t>
+          <t>partner_favorite_color_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_15,_'label':_'student',_'value':_'student'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 15, 'label': 'Student', 'value': 'student'}</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>partner_hobbies_choices</t>
+          <t>partner_favorite_color_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>partner_hobbies_choices</t>
+          <t>partner_favorite_color_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yellow</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yellow</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>partner_education_choices</t>
+          <t>partner_favorite_color_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_9,_'label':_'employed',_'value':_'employed'}</t>
+          <t>purple</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 9, 'label': 'Employed', 'value': 'employed'}</t>
+          <t>Purple</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>partner_education_choices</t>
+          <t>partner_favorite_sport_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'self',_'value':_'self'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'Self', 'value': 'self'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>partner_education_choices</t>
+          <t>partner_favorite_sport_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'retired',_'value':_'retired'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'Retired', 'value': 'retired'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>partner_education_choices</t>
+          <t>partner_favorite_destination_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_12,_'label':_'disabled',_'value':_'disabled'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 12, 'label': 'Disabled', 'value': 'disabled'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>partner_education_choices</t>
+          <t>partner_favorite_destination_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_13,_'label':_'deceased',_'value':_'deceased'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 13, 'label': 'Deceased', 'value': 'deceased'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>partner_education_choices</t>
+          <t>partner_favorite_destination_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_15,_'label':_'student',_'value':_'student',_'value2':_none}</t>
+          <t>sometime</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 15, 'label': 'Student', 'value': 'student', 'value2': None}</t>
+          <t>Sometime</t>
         </is>
       </c>
     </row>
